--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,56 +904,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136867875</v>
+        <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>100012</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222306</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärnstarr</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex echinata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Murray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mänttorp N om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Mänttorp NO om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517865</v>
+        <v>517940</v>
       </c>
       <c r="R4" t="n">
-        <v>6635928</v>
+        <v>6635890</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,24 +984,33 @@
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,10 +1024,467 @@
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137008825</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137008948</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106528</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mänttorp NO om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517926</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6635993</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137008948</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136867875</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100012</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mänttorp N om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517865</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6635928</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136867875</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137008951</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100012</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mänttorp NO om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517926</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6635993</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137008951</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137008930</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mänttorp NO om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517926</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6635993</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137008930</t>
         </is>
       </c>
     </row>
@@ -1023,6 +1493,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100012</v>
+        <v>100018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100012</v>
+        <v>100018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100018</v>
+        <v>100020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100018</v>
+        <v>100020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100020</v>
+        <v>100021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100020</v>
+        <v>100021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100021</v>
+        <v>100027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100021</v>
+        <v>100027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100027</v>
+        <v>100031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100027</v>
+        <v>100031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100031</v>
+        <v>100033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100031</v>
+        <v>100033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100033</v>
+        <v>100035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100033</v>
+        <v>100035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100035</v>
+        <v>100048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100035</v>
+        <v>100048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100048</v>
+        <v>100050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100048</v>
+        <v>100050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -939,11 +939,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1178,11 +1174,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1294,11 +1286,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1405,11 +1393,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100050</v>
+        <v>100053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100050</v>
+        <v>100053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100053</v>
+        <v>100063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100053</v>
+        <v>100063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100063</v>
+        <v>100064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100063</v>
+        <v>100064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100064</v>
+        <v>100069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100064</v>
+        <v>100069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100069</v>
+        <v>100072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100069</v>
+        <v>100072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100072</v>
+        <v>100078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100072</v>
+        <v>100078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100078</v>
+        <v>100090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100078</v>
+        <v>100090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136867829</v>
       </c>
       <c r="B2" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867849</v>
       </c>
       <c r="B3" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136867875</v>
       </c>
       <c r="B6" t="n">
-        <v>100090</v>
+        <v>100091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100090</v>
+        <v>100091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100091</v>
+        <v>100094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106622</v>
+        <v>106624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100094</v>
+        <v>100095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27914-2026 artfynd.xlsx
+++ b/artfynd/A 27914-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137008825</v>
       </c>
       <c r="B4" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137008948</v>
       </c>
       <c r="B5" t="n">
-        <v>106624</v>
+        <v>106628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137008951</v>
       </c>
       <c r="B7" t="n">
-        <v>100095</v>
+        <v>100098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137008930</v>
       </c>
       <c r="B8" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
